--- a/E/BKC01D.xlsx
+++ b/E/BKC01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="251">
   <si>
     <t/>
   </si>
@@ -241,52 +241,100 @@
     <t>KDOMO B.WASH STR 200</t>
   </si>
   <si>
+    <t>20113805</t>
+  </si>
+  <si>
+    <t>KDOMO B.WASH ORG 200</t>
+  </si>
+  <si>
+    <t>20143473</t>
+  </si>
+  <si>
+    <t>B&amp;B S&amp;C GLY SH200+50</t>
+  </si>
+  <si>
+    <t>20143316</t>
+  </si>
+  <si>
+    <t>ZWTSL B/B ANTIBAC300</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20012094</t>
+  </si>
+  <si>
+    <t>ZWITSAL B/BATH MH300</t>
+  </si>
+  <si>
+    <t>20143472</t>
+  </si>
+  <si>
+    <t>BB HAIR&amp;BW PMP240+60</t>
+  </si>
+  <si>
+    <t>20135607</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC LVELY100</t>
+  </si>
+  <si>
+    <t>20113917</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC SWT 100</t>
+  </si>
+  <si>
+    <t>20113918</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC FRSH100</t>
+  </si>
+  <si>
+    <t>20143470</t>
+  </si>
+  <si>
+    <t>B&amp;B SPRAY CLGNE80+20</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20143330</t>
+  </si>
+  <si>
+    <t>B&amp;B HAIR LT SPRY100</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20090401</t>
+  </si>
+  <si>
+    <t>KDOMO SH&amp;CON BLU 200</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20134006</t>
   </si>
   <si>
     <t>KDOMO SH&amp;CON CHRY200</t>
   </si>
   <si>
-    <t>20090401</t>
-  </si>
-  <si>
-    <t>KDOMO SH&amp;CON BLU 200</t>
-  </si>
-  <si>
-    <t>20113805</t>
-  </si>
-  <si>
-    <t>KDOMO B.WASH ORG 200</t>
-  </si>
-  <si>
-    <t>20143473</t>
-  </si>
-  <si>
-    <t>B&amp;B S&amp;C GLY SH200+50</t>
-  </si>
-  <si>
-    <t>20143472</t>
-  </si>
-  <si>
-    <t>BB HAIR&amp;BW PMP240+60</t>
-  </si>
-  <si>
-    <t>20135607</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC LVELY100</t>
-  </si>
-  <si>
-    <t>20113917</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC SWT 100</t>
-  </si>
-  <si>
-    <t>20113918</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC FRSH100</t>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20130478</t>
+  </si>
+  <si>
+    <t>DOREMI COLG GLACR100</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>20008706</t>
@@ -295,25 +343,7 @@
     <t>MASTER CLG SPRMN 100</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20130478</t>
-  </si>
-  <si>
-    <t>DOREMI COLG GLACR100</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20143470</t>
-  </si>
-  <si>
-    <t>B&amp;B SPRAY CLGNE80+20</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>19</t>
   </si>
   <si>
     <t>20135794</t>
@@ -598,9 +628,6 @@
     <t>CUSSONS B/CRM MILD50</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>20005584</t>
   </si>
   <si>
@@ -611,9 +638,6 @@
   </si>
   <si>
     <t>ZWTSAL B.BATH R.H400</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20110812</t>
@@ -1132,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1760,7 +1784,7 @@
         <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1780,15 +1804,15 @@
         <v>29</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1800,15 +1824,15 @@
         <v>32</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1825,10 +1849,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1845,10 +1869,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1865,10 +1889,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1885,10 +1909,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1897,18 +1921,18 @@
         <v>12</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1917,18 +1941,18 @@
         <v>12</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1937,7 +1961,7 @@
         <v>12</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>23</v>
@@ -1945,39 +1969,39 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>9</v>
@@ -1985,19 +2009,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>9</v>
@@ -2005,10 +2029,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2017,18 +2041,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2037,18 +2061,18 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2057,18 +2081,18 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2077,18 +2101,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2097,18 +2121,18 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2117,18 +2141,18 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2137,18 +2161,18 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2157,18 +2181,18 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2177,18 +2201,18 @@
         <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2197,18 +2221,18 @@
         <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2217,18 +2241,18 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2237,78 +2261,78 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2317,18 +2341,18 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2337,18 +2361,18 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2357,18 +2381,18 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2377,18 +2401,18 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2397,18 +2421,18 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2417,18 +2441,18 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2437,18 +2461,18 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2457,18 +2481,18 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2477,18 +2501,18 @@
         <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2497,78 +2521,78 @@
         <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2577,18 +2601,18 @@
         <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2597,18 +2621,18 @@
         <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>9</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2617,7 +2641,7 @@
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>9</v>
@@ -2625,10 +2649,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2637,7 +2661,7 @@
         <v>22</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>9</v>
@@ -2645,10 +2669,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2657,7 +2681,7 @@
         <v>22</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>9</v>
@@ -2665,10 +2689,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2677,7 +2701,7 @@
         <v>22</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>9</v>
@@ -2685,10 +2709,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2697,18 +2721,18 @@
         <v>22</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2717,18 +2741,18 @@
         <v>22</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2737,7 +2761,7 @@
         <v>22</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>9</v>
@@ -2745,10 +2769,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2757,18 +2781,18 @@
         <v>22</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2777,18 +2801,18 @@
         <v>22</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2797,18 +2821,18 @@
         <v>22</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2817,18 +2841,18 @@
         <v>22</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2837,27 +2861,27 @@
         <v>22</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>38</v>
@@ -2865,50 +2889,50 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -2917,18 +2941,18 @@
         <v>26</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -2937,18 +2961,18 @@
         <v>26</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -2957,18 +2981,18 @@
         <v>26</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -2977,7 +3001,7 @@
         <v>26</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>9</v>
@@ -2985,10 +3009,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -2997,7 +3021,7 @@
         <v>26</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>9</v>
@@ -3005,10 +3029,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3017,18 +3041,18 @@
         <v>26</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3037,7 +3061,7 @@
         <v>26</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>9</v>
@@ -3045,10 +3069,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3057,7 +3081,7 @@
         <v>26</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>9</v>
@@ -3065,39 +3089,39 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>9</v>
@@ -3105,19 +3129,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>9</v>
@@ -3125,10 +3149,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3137,18 +3161,18 @@
         <v>29</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3157,18 +3181,18 @@
         <v>29</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3177,18 +3201,18 @@
         <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3197,7 +3221,7 @@
         <v>29</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>38</v>
@@ -3205,10 +3229,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3217,18 +3241,18 @@
         <v>29</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3237,18 +3261,18 @@
         <v>29</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3257,18 +3281,18 @@
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3277,18 +3301,18 @@
         <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3297,9 +3321,69 @@
         <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F111" s="1" t="s">
         <v>5</v>
       </c>
     </row>
